--- a/result/Table202508.xlsx
+++ b/result/Table202508.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
         <v>57.28</v>
       </c>
       <c r="J2" t="n">
-        <v>70.31999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="K2" t="n">
-        <v>22.77</v>
+        <v>40.62</v>
       </c>
       <c r="L2" t="n">
-        <v>22765.36</v>
+        <v>40625</v>
       </c>
     </row>
     <row r="3">
@@ -562,24 +562,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>31.85</v>
       </c>
       <c r="J3" t="n">
-        <v>32.59</v>
+        <v>30.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2.32</v>
+        <v>-2.98</v>
       </c>
       <c r="L3" t="n">
-        <v>2323.39</v>
+        <v>-2982.73</v>
       </c>
     </row>
     <row r="4">
@@ -904,24 +904,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>10.49</v>
       </c>
       <c r="J10" t="n">
-        <v>9.91</v>
+        <v>9.31</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.53</v>
+        <v>-11.25</v>
       </c>
       <c r="L10" t="n">
-        <v>-5529.08</v>
+        <v>-11248.81</v>
       </c>
     </row>
     <row r="11">
@@ -1146,24 +1146,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
         <v>59.89</v>
       </c>
       <c r="J15" t="n">
-        <v>58.81</v>
+        <v>54.05</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.8</v>
+        <v>-9.75</v>
       </c>
       <c r="L15" t="n">
-        <v>-1803.31</v>
+        <v>-9751.209999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1242,24 +1242,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
         <v>32.9</v>
       </c>
       <c r="J17" t="n">
-        <v>30.26</v>
+        <v>28.34</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.02</v>
+        <v>-13.86</v>
       </c>
       <c r="L17" t="n">
-        <v>-8024.32</v>
+        <v>-13860.18</v>
       </c>
     </row>
     <row r="18">
@@ -1288,24 +1288,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>27.67</v>
       </c>
       <c r="J18" t="n">
-        <v>26.03</v>
+        <v>24.88</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.93</v>
+        <v>-10.08</v>
       </c>
       <c r="L18" t="n">
-        <v>-5927</v>
+        <v>-10083.12</v>
       </c>
     </row>
     <row r="19">
@@ -1626,24 +1626,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
         <v>9.369999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>8.859999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.44</v>
+        <v>-11.21</v>
       </c>
       <c r="L25" t="n">
-        <v>-5442.9</v>
+        <v>-11205.98</v>
       </c>
     </row>
     <row r="26">
@@ -1672,24 +1672,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
         <v>46.4</v>
       </c>
       <c r="J26" t="n">
-        <v>44.46</v>
+        <v>40.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.18</v>
+        <v>-12.72</v>
       </c>
       <c r="L26" t="n">
-        <v>-4181.03</v>
+        <v>-12715.52</v>
       </c>
     </row>
     <row r="27">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
         <v>13.13</v>
       </c>
       <c r="J31" t="n">
-        <v>12.23</v>
+        <v>11.72</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.85</v>
+        <v>-10.74</v>
       </c>
       <c r="L31" t="n">
-        <v>-6854.53</v>
+        <v>-10738.77</v>
       </c>
     </row>
     <row r="32">
@@ -2160,24 +2160,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
         <v>23.31</v>
       </c>
       <c r="J36" t="n">
-        <v>24.69</v>
+        <v>22.93</v>
       </c>
       <c r="K36" t="n">
-        <v>5.92</v>
+        <v>-1.63</v>
       </c>
       <c r="L36" t="n">
-        <v>5920.21</v>
+        <v>-1630.2</v>
       </c>
     </row>
     <row r="37">
@@ -2206,24 +2206,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>93.7</v>
       </c>
       <c r="J37" t="n">
-        <v>92.34999999999999</v>
+        <v>86.48</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.44</v>
+        <v>-7.71</v>
       </c>
       <c r="L37" t="n">
-        <v>-1440.77</v>
+        <v>-7705.44</v>
       </c>
     </row>
     <row r="38">
@@ -2348,24 +2348,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
         <v>44.68</v>
       </c>
       <c r="J40" t="n">
-        <v>46.81</v>
+        <v>57.97</v>
       </c>
       <c r="K40" t="n">
-        <v>4.77</v>
+        <v>29.74</v>
       </c>
       <c r="L40" t="n">
-        <v>4767.23</v>
+        <v>29744.85</v>
       </c>
     </row>
     <row r="41">
@@ -2394,24 +2394,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I41" t="n">
         <v>89.5</v>
       </c>
       <c r="J41" t="n">
-        <v>83.01000000000001</v>
+        <v>142.93</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.25</v>
+        <v>59.7</v>
       </c>
       <c r="L41" t="n">
-        <v>-7251.4</v>
+        <v>59698.32</v>
       </c>
     </row>
     <row r="42">
@@ -2636,24 +2636,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I46" t="n">
         <v>25.16</v>
       </c>
       <c r="J46" t="n">
-        <v>23.73</v>
+        <v>23.12</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.68</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>-5683.62</v>
+        <v>-8108.11</v>
       </c>
     </row>
     <row r="47">
@@ -2732,24 +2732,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" t="n">
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>37.84</v>
+        <v>33.02</v>
       </c>
       <c r="K48" t="n">
-        <v>30.48</v>
+        <v>13.86</v>
       </c>
       <c r="L48" t="n">
-        <v>30482.76</v>
+        <v>13862.07</v>
       </c>
     </row>
     <row r="49">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I49" t="n">
         <v>69.58</v>
       </c>
       <c r="J49" t="n">
-        <v>65.93000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.25</v>
+        <v>-12.04</v>
       </c>
       <c r="L49" t="n">
-        <v>-5245.76</v>
+        <v>-12043.69</v>
       </c>
     </row>
     <row r="50">
@@ -3116,24 +3116,24 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I56" t="n">
         <v>26.5</v>
       </c>
       <c r="J56" t="n">
-        <v>25.19</v>
+        <v>23.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.94</v>
+        <v>-10.26</v>
       </c>
       <c r="L56" t="n">
-        <v>-4943.4</v>
+        <v>-10264.15</v>
       </c>
     </row>
     <row r="57">
@@ -3212,24 +3212,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I58" t="n">
         <v>23.87</v>
       </c>
       <c r="J58" t="n">
-        <v>22.68</v>
+        <v>21.46</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.99</v>
+        <v>-10.1</v>
       </c>
       <c r="L58" t="n">
-        <v>-4985.34</v>
+        <v>-10096.36</v>
       </c>
     </row>
     <row r="59">
@@ -3308,24 +3308,24 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I60" t="n">
         <v>12.85</v>
       </c>
       <c r="J60" t="n">
-        <v>12.56</v>
+        <v>11.89</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.26</v>
+        <v>-7.47</v>
       </c>
       <c r="L60" t="n">
-        <v>-2256.81</v>
+        <v>-7470.82</v>
       </c>
     </row>
     <row r="61">
@@ -3400,24 +3400,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I62" t="n">
         <v>4.08</v>
       </c>
       <c r="J62" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.41</v>
+        <v>-8.33</v>
       </c>
       <c r="L62" t="n">
-        <v>-4411.76</v>
+        <v>-8333.33</v>
       </c>
     </row>
     <row r="63">
@@ -3546,24 +3546,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" t="n">
         <v>4.2</v>
       </c>
       <c r="J65" t="n">
-        <v>4.69</v>
+        <v>4.28</v>
       </c>
       <c r="K65" t="n">
-        <v>11.67</v>
+        <v>1.9</v>
       </c>
       <c r="L65" t="n">
-        <v>11666.67</v>
+        <v>1904.76</v>
       </c>
     </row>
     <row r="66">
